--- a/data/trans_dic/IP12-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP12-Habitat-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que limitaron su actividad por dolores o síntomas</t>
+          <t>Menores que limitaron su actividad por dolores o síntomas (tasa de respuesta: 99,99%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,61; 13,63</t>
+          <t>5,42; 12,95</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8,25; 17,92</t>
+          <t>7,92; 17,47</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,52; 10,77</t>
+          <t>3,42; 11,5</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,31; 12,69</t>
+          <t>4,29; 13,05</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,62; 11,52</t>
+          <t>4,66; 11,49</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,53; 10,28</t>
+          <t>3,75; 10,71</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,24; 8,91</t>
+          <t>2,31; 8,86</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,11; 10,68</t>
+          <t>3,52; 11,29</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,82; 11,09</t>
+          <t>6,09; 11,05</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6,6; 12,75</t>
+          <t>6,72; 12,25</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3,64; 8,46</t>
+          <t>3,72; 8,65</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,74; 10,11</t>
+          <t>4,57; 9,78</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,52; 9,01</t>
+          <t>3,98; 9,31</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,61; 13,28</t>
+          <t>6,23; 12,72</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,15; 13,08</t>
+          <t>7,0; 13,3</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,61; 10,87</t>
+          <t>4,45; 10,57</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,36; 11,46</t>
+          <t>5,37; 11,62</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,86; 9,58</t>
+          <t>3,97; 9,66</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,59; 10,6</t>
+          <t>4,75; 10,16</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,6; 10,14</t>
+          <t>4,38; 9,89</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,24; 9,13</t>
+          <t>5,33; 9,3</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5,66; 9,94</t>
+          <t>5,87; 10,26</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6,55; 10,82</t>
+          <t>6,59; 10,83</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>5,3; 9,1</t>
+          <t>5,07; 9,13</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,97; 13,78</t>
+          <t>5,76; 13,63</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,62; 9,78</t>
+          <t>3,69; 10,1</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,06; 11,75</t>
+          <t>4,88; 11,7</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,0; 11,61</t>
+          <t>4,25; 11,42</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,02; 9,19</t>
+          <t>3,28; 9,28</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,58; 15,5</t>
+          <t>7,45; 15,33</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,26; 13,69</t>
+          <t>5,97; 13,79</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,27; 14,11</t>
+          <t>5,45; 14,52</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,98; 10,29</t>
+          <t>5,16; 9,86</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6,17; 11,49</t>
+          <t>6,16; 11,33</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6,58; 11,63</t>
+          <t>6,47; 11,6</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5,37; 11,42</t>
+          <t>5,78; 11,44</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,43; 5,83</t>
+          <t>1,72; 6,12</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,8; 11,07</t>
+          <t>4,8; 10,82</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,39; 10,16</t>
+          <t>4,28; 10,51</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,6; 9,78</t>
+          <t>3,5; 9,29</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,12; 8,03</t>
+          <t>2,99; 7,94</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,01; 14,18</t>
+          <t>6,9; 14,66</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,43; 7,07</t>
+          <t>2,64; 7,53</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,4; 13,66</t>
+          <t>5,82; 13,86</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,75; 5,93</t>
+          <t>2,71; 6,18</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6,66; 11,43</t>
+          <t>6,72; 11,18</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3,98; 8,0</t>
+          <t>4,02; 7,98</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5,71; 10,39</t>
+          <t>5,49; 10,49</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,04; 8,15</t>
+          <t>5,03; 8,08</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,04; 10,37</t>
+          <t>7,05; 10,49</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,25; 9,63</t>
+          <t>6,33; 9,62</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5,52; 8,98</t>
+          <t>5,41; 8,92</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,14; 8,07</t>
+          <t>5,26; 8,01</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,82; 10,27</t>
+          <t>6,8; 10,13</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,06; 8,05</t>
+          <t>5,21; 8,19</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>6,08; 9,74</t>
+          <t>6,25; 9,82</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,44; 7,59</t>
+          <t>5,45; 7,64</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7,47; 10,0</t>
+          <t>7,37; 9,91</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6,07; 8,36</t>
+          <t>6,23; 8,39</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,25; 8,73</t>
+          <t>6,28; 8,91</t>
         </is>
       </c>
     </row>
@@ -1356,4 +1357,1204 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que limitaron su actividad por dolores o síntomas (tasa de respuesta: 99,99%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>12241</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>17142</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>8872</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>8853</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>11787</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>10211</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>7118</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>8855</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>24028</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>27354</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>15991</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>17707</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>7520; 17961</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>11036; 24344</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>4577; 15379</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>5028; 15309</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>7126; 17590</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>5800; 16559</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>3424; 13122</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>4936; 15851</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>17776; 32237</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>19773; 36018</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>10469; 24377</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>11769; 25201</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>12094</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>19183</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>20274</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>13592</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>16832</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>14126</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>16181</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>17222</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>28927</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>33309</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>36455</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>30814</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>7765; 18171</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>12855; 26255</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>14459; 27492</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>8486; 20134</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>11390; 24660</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>8890; 21623</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>10651; 22802</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>11172; 25214</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>21719; 37884</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>25254; 44144</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>28385; 46664</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>22589; 40673</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>12697</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>9416</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>12193</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>14514</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>8278</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>18117</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>15943</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>16077</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>20975</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>27533</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>28136</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>30592</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>7940; 18782</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>5730; 15690</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>7607; 18253</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>8055; 21653</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>4913; 13882</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>12410; 25532</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>9955; 22985</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>10107; 26905</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>14830; 28340</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>19837; 36492</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>20886; 37434</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>21656; 42896</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>6845</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>15551</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>14386</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>10313</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>10495</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>21106</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>9240</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>16950</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>17340</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>36656</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>23627</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>27263</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>3597; 12805</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>10084; 22763</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>8886; 21798</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>5881; 15606</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>6212; 16495</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>14370; 30541</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>5433; 15495</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>10552; 25125</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>11306; 25785</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>28120; 46799</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>16595; 32983</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>19186; 36636</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>157</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>43878</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>61292</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>55726</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>47272</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>47392</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>63560</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>48482</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>59103</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>91270</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>124852</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>104208</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>106375</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>34289; 55048</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>50187; 74651</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>44576; 67704</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>35978; 59317</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>38030; 57921</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>51223; 76314</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>38826; 61026</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>47607; 74856</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>76515; 107244</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>107969; 145150</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>90269; 121541</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>89665; 127135</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP12-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP12-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que limitaron su actividad por dolores o síntomas (tasa de respuesta: 99,99%)</t>
+          <t>Menores que en las últimas 2 semanas limitaron su actividad por dolores o síntomas (tasa de respuesta: 99,99%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,42; 12,95</t>
+          <t>5,11; 13,35</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7,92; 17,47</t>
+          <t>8,37; 17,66</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,42; 11,5</t>
+          <t>3,61; 11,53</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,29; 13,05</t>
+          <t>4,51; 12,29</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,66; 11,49</t>
+          <t>4,52; 12,07</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,75; 10,71</t>
+          <t>3,86; 10,87</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,31; 8,86</t>
+          <t>2,38; 9,65</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,52; 11,29</t>
+          <t>3,48; 11,18</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6,09; 11,05</t>
+          <t>5,65; 11,07</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6,72; 12,25</t>
+          <t>6,62; 12,69</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3,72; 8,65</t>
+          <t>3,6; 8,41</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,57; 9,78</t>
+          <t>4,62; 9,93</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,98; 9,31</t>
+          <t>3,88; 8,93</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,23; 12,72</t>
+          <t>6,39; 13,34</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,0; 13,3</t>
+          <t>7,14; 13,48</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,45; 10,57</t>
+          <t>4,59; 10,68</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,37; 11,62</t>
+          <t>5,09; 11,27</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,97; 9,66</t>
+          <t>3,81; 9,54</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,75; 10,16</t>
+          <t>4,71; 10,62</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,38; 9,89</t>
+          <t>4,37; 9,84</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,33; 9,3</t>
+          <t>5,25; 9,46</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5,87; 10,26</t>
+          <t>5,93; 10,0</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6,59; 10,83</t>
+          <t>6,62; 10,75</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>5,07; 9,13</t>
+          <t>5,17; 9,29</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,76; 13,63</t>
+          <t>6,24; 13,7</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,69; 10,1</t>
+          <t>3,54; 9,89</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,88; 11,7</t>
+          <t>4,99; 12,15</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,25; 11,42</t>
+          <t>4,37; 11,86</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,28; 9,28</t>
+          <t>3,07; 9,34</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,45; 15,33</t>
+          <t>7,64; 15,26</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,97; 13,79</t>
+          <t>6,45; 13,98</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,45; 14,52</t>
+          <t>4,95; 13,77</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,16; 9,86</t>
+          <t>5,1; 9,86</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6,16; 11,33</t>
+          <t>6,49; 11,34</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6,47; 11,6</t>
+          <t>6,33; 11,42</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5,78; 11,44</t>
+          <t>5,61; 11,64</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,72; 6,12</t>
+          <t>1,43; 5,94</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,8; 10,82</t>
+          <t>4,86; 11,24</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,28; 10,51</t>
+          <t>4,42; 10,28</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,5; 9,29</t>
+          <t>3,57; 9,56</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,99; 7,94</t>
+          <t>2,85; 7,72</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,9; 14,66</t>
+          <t>7,02; 14,2</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,64; 7,53</t>
+          <t>2,41; 7,52</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5,82; 13,86</t>
+          <t>6,05; 13,78</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,71; 6,18</t>
+          <t>2,86; 6,2</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6,72; 11,18</t>
+          <t>6,64; 11,58</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4,02; 7,98</t>
+          <t>4,01; 7,84</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5,49; 10,49</t>
+          <t>5,65; 10,59</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,03; 8,08</t>
+          <t>5,05; 8,16</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,05; 10,49</t>
+          <t>6,95; 10,52</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,33; 9,62</t>
+          <t>6,34; 9,67</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5,41; 8,92</t>
+          <t>5,56; 8,8</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,26; 8,01</t>
+          <t>5,19; 8,12</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,8; 10,13</t>
+          <t>7,0; 10,27</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,21; 8,19</t>
+          <t>5,14; 8,1</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>6,25; 9,82</t>
+          <t>6,02; 9,55</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,45; 7,64</t>
+          <t>5,58; 7,65</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7,37; 9,91</t>
+          <t>7,37; 9,86</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6,23; 8,39</t>
+          <t>6,15; 8,38</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,28; 8,91</t>
+          <t>6,31; 8,82</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que limitaron su actividad por dolores o síntomas (tasa de respuesta: 99,99%)</t>
+          <t>Menores que en las últimas 2 semanas limitaron su actividad por dolores o síntomas (tasa de respuesta: 99,99%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>7520; 17961</t>
+          <t>7086; 18513</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>11036; 24344</t>
+          <t>11667; 24611</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4577; 15379</t>
+          <t>4829; 15417</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5028; 15309</t>
+          <t>5289; 14408</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>7126; 17590</t>
+          <t>6916; 18476</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5800; 16559</t>
+          <t>5969; 16812</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3424; 13122</t>
+          <t>3524; 14286</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4936; 15851</t>
+          <t>4888; 15693</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>17776; 32237</t>
+          <t>16494; 32305</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>19773; 36018</t>
+          <t>19452; 37313</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10469; 24377</t>
+          <t>10153; 23684</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>11769; 25201</t>
+          <t>11894; 25600</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7765; 18171</t>
+          <t>7572; 17419</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12855; 26255</t>
+          <t>13187; 27523</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14459; 27492</t>
+          <t>14756; 27852</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8486; 20134</t>
+          <t>8749; 20346</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>11390; 24660</t>
+          <t>10791; 23915</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8890; 21623</t>
+          <t>8531; 21348</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10651; 22802</t>
+          <t>10562; 23830</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>11172; 25214</t>
+          <t>11141; 25084</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>21719; 37884</t>
+          <t>21371; 38522</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>25254; 44144</t>
+          <t>25509; 43019</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>28385; 46664</t>
+          <t>28533; 46336</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>22589; 40673</t>
+          <t>23044; 41406</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>7940; 18782</t>
+          <t>8606; 18886</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>5730; 15690</t>
+          <t>5501; 15365</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7607; 18253</t>
+          <t>7786; 18956</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8055; 21653</t>
+          <t>8279; 22488</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>4913; 13882</t>
+          <t>4589; 13978</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12410; 25532</t>
+          <t>12733; 25416</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9955; 22985</t>
+          <t>10750; 23295</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>10107; 26905</t>
+          <t>9172; 25506</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>14830; 28340</t>
+          <t>14668; 28351</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>19837; 36492</t>
+          <t>20883; 36498</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>20886; 37434</t>
+          <t>20437; 36836</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>21656; 42896</t>
+          <t>21048; 43627</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3597; 12805</t>
+          <t>3002; 12437</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>10084; 22763</t>
+          <t>10219; 23630</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>8886; 21798</t>
+          <t>9170; 21315</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5881; 15606</t>
+          <t>5999; 16051</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6212; 16495</t>
+          <t>5929; 16052</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>14370; 30541</t>
+          <t>14631; 29585</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5433; 15495</t>
+          <t>4955; 15471</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>10552; 25125</t>
+          <t>10961; 24967</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>11306; 25785</t>
+          <t>11912; 25882</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>28120; 46799</t>
+          <t>27813; 48487</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>16595; 32983</t>
+          <t>16563; 32377</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>19186; 36636</t>
+          <t>19742; 36971</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>34289; 55048</t>
+          <t>34365; 55556</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>50187; 74651</t>
+          <t>49428; 74848</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>44576; 67704</t>
+          <t>44619; 68026</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>35978; 59317</t>
+          <t>37016; 58539</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>38030; 57921</t>
+          <t>37521; 58690</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>51223; 76314</t>
+          <t>52770; 77354</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>38826; 61026</t>
+          <t>38294; 60359</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>47607; 74856</t>
+          <t>45885; 72733</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>76515; 107244</t>
+          <t>78269; 107397</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>107969; 145150</t>
+          <t>107955; 144490</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>90269; 121541</t>
+          <t>89092; 121457</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>89665; 127135</t>
+          <t>90023; 125932</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP12-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP12-Habitat-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>7,7%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>6,6%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>4,81%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>6,65%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>8,82%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>12,3%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>6,64%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>7,55%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>7,7%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>6,6%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>4,81%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>7,07%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,11; 13,35</t>
+          <t>4,62; 11,52</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8,37; 17,66</t>
+          <t>3,53; 10,28</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,61; 11,53</t>
+          <t>2,24; 8,91</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,51; 12,29</t>
+          <t>3,36; 11,29</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,52; 12,07</t>
+          <t>5,61; 13,63</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,86; 10,87</t>
+          <t>8,25; 17,92</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,38; 9,65</t>
+          <t>3,52; 10,77</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,48; 11,18</t>
+          <t>4,3; 12,52</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,65; 11,07</t>
+          <t>5,82; 11,09</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6,62; 12,69</t>
+          <t>6,6; 12,75</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3,6; 8,41</t>
+          <t>3,64; 8,46</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,62; 9,93</t>
+          <t>4,82; 10,29</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>7,93%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>6,31%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>7,21%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>6,87%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>6,2%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>9,3%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>9,81%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>7,13%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>7,93%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>6,31%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>7,21%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,89%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,88; 8,93</t>
+          <t>5,36; 11,46</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,39; 13,34</t>
+          <t>3,86; 9,58</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,14; 13,48</t>
+          <t>4,59; 10,6</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,59; 10,68</t>
+          <t>4,75; 10,32</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,09; 11,27</t>
+          <t>3,52; 9,01</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,81; 9,54</t>
+          <t>6,61; 13,28</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,71; 10,62</t>
+          <t>7,15; 13,08</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,37; 9,84</t>
+          <t>4,5; 10,73</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,25; 9,46</t>
+          <t>5,24; 9,13</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5,93; 10,0</t>
+          <t>5,66; 9,94</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6,62; 10,75</t>
+          <t>6,55; 10,82</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>5,17; 9,29</t>
+          <t>5,31; 9,11</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>5,53%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>10,88%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>9,57%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>9,2%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>9,21%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>6,06%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>7,82%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>7,66%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>5,53%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>10,88%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>9,57%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>9,28%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,24; 13,7</t>
+          <t>3,02; 9,19</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,54; 9,89</t>
+          <t>7,58; 15,5</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,99; 12,15</t>
+          <t>6,26; 13,69</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,37; 11,86</t>
+          <t>5,63; 15,3</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,07; 9,34</t>
+          <t>5,97; 13,78</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,64; 15,26</t>
+          <t>3,62; 9,78</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,45; 13,98</t>
+          <t>5,06; 11,75</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,95; 13,77</t>
+          <t>5,84; 14,01</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,1; 9,86</t>
+          <t>4,98; 10,29</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6,49; 11,34</t>
+          <t>6,17; 11,49</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6,33; 11,42</t>
+          <t>6,58; 11,63</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5,61; 11,64</t>
+          <t>6,52; 12,67</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>5,05%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>10,13%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>4,49%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>9,0%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>3,27%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>7,39%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>6,94%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>6,14%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>5,05%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>10,13%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>4,49%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,56%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,43; 5,94</t>
+          <t>3,12; 8,03</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,86; 11,24</t>
+          <t>7,01; 14,18</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,42; 10,28</t>
+          <t>2,43; 7,07</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,57; 9,56</t>
+          <t>6,08; 13,06</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,85; 7,72</t>
+          <t>1,43; 5,83</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,02; 14,2</t>
+          <t>4,8; 11,07</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,41; 7,52</t>
+          <t>4,39; 10,16</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,05; 13,78</t>
+          <t>3,67; 9,72</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,86; 6,2</t>
+          <t>2,75; 5,93</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6,64; 11,58</t>
+          <t>6,66; 11,43</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4,01; 7,84</t>
+          <t>3,98; 8,0</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5,65; 10,59</t>
+          <t>5,54; 10,09</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>6,56%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>8,44%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>6,51%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>7,91%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>6,44%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>8,62%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>7,92%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>7,1%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>6,56%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>8,44%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>6,51%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,68%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,05; 8,16</t>
+          <t>5,14; 8,07</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,95; 10,52</t>
+          <t>6,82; 10,27</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,34; 9,67</t>
+          <t>5,06; 8,05</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5,56; 8,8</t>
+          <t>6,23; 10,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,19; 8,12</t>
+          <t>5,04; 8,15</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,0; 10,27</t>
+          <t>7,04; 10,37</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,14; 8,1</t>
+          <t>6,25; 9,63</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>6,02; 9,55</t>
+          <t>5,78; 9,39</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,58; 7,65</t>
+          <t>5,44; 7,59</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7,37; 9,86</t>
+          <t>7,47; 10,0</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6,15; 8,38</t>
+          <t>6,07; 8,36</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,31; 8,82</t>
+          <t>6,47; 9,05</t>
         </is>
       </c>
     </row>
@@ -1393,7 +1393,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1401,7 +1401,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1514,37 +1514,37 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>16</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1577,42 +1577,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>11787</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>10211</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>7118</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>8367</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>12241</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>17142</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>8872</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>8853</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>11787</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>10211</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>7118</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8855</t>
+          <t>9096</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>17707</t>
+          <t>17463</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>7086; 18513</t>
+          <t>7072; 17641</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>11667; 24611</t>
+          <t>5459; 15909</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4829; 15417</t>
+          <t>3318; 13198</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5289; 14408</t>
+          <t>4227; 14212</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>6916; 18476</t>
+          <t>7777; 18905</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5969; 16812</t>
+          <t>11502; 24974</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3524; 14286</t>
+          <t>4710; 14406</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4888; 15693</t>
+          <t>5201; 15156</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>16494; 32305</t>
+          <t>16987; 32361</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>19452; 37313</t>
+          <t>19413; 37478</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10153; 23684</t>
+          <t>10245; 23831</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>11894; 25600</t>
+          <t>11917; 25405</t>
         </is>
       </c>
     </row>
@@ -1717,42 +1717,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>22</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1785,42 +1785,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>16832</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>14126</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>16181</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>16306</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>12094</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>19183</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>20274</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>13592</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>16832</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>14126</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>16181</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>17222</t>
+          <t>12725</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>30814</t>
+          <t>29031</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7572; 17419</t>
+          <t>11380; 24304</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>13187; 27523</t>
+          <t>8632; 21435</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14756; 27852</t>
+          <t>10303; 23793</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8749; 20346</t>
+          <t>11268; 24473</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>10791; 23915</t>
+          <t>6863; 17587</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8531; 21348</t>
+          <t>13640; 27400</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10562; 23830</t>
+          <t>14780; 27021</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>11141; 25084</t>
+          <t>8301; 19791</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>21371; 38522</t>
+          <t>21330; 37202</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>25509; 43019</t>
+          <t>24363; 42771</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>28533; 46336</t>
+          <t>28221; 46639</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>23044; 41406</t>
+          <t>22400; 38410</t>
         </is>
       </c>
     </row>
@@ -1925,42 +1925,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>23</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1993,42 +1993,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>8278</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>18117</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>15943</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>15483</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>12697</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>9416</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>12193</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>14514</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>8278</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>18117</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>15943</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>16077</t>
+          <t>14649</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>30592</t>
+          <t>30132</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>8606; 18886</t>
+          <t>4519; 13756</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>5501; 15365</t>
+          <t>12628; 25828</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7786; 18956</t>
+          <t>10433; 22825</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8279; 22488</t>
+          <t>9481; 25763</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>4589; 13978</t>
+          <t>8225; 18991</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12733; 25416</t>
+          <t>5627; 15190</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10750; 23295</t>
+          <t>7898; 18323</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>9172; 25506</t>
+          <t>9119; 21887</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>14668; 28351</t>
+          <t>14315; 29592</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>20883; 36498</t>
+          <t>19862; 36989</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>20437; 36836</t>
+          <t>21241; 37541</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>21048; 43627</t>
+          <t>21151; 41126</t>
         </is>
       </c>
     </row>
@@ -2133,42 +2133,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>16</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2201,42 +2201,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>10495</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>21106</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>9240</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>15249</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>6845</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>15551</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>14386</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>10313</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>10495</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>21106</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>9240</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>16950</t>
+          <t>10178</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>27263</t>
+          <t>25427</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3002; 12437</t>
+          <t>6474; 16685</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>10219; 23630</t>
+          <t>14601; 29557</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>9170; 21315</t>
+          <t>4998; 14555</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5999; 16051</t>
+          <t>10295; 22116</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5929; 16052</t>
+          <t>2992; 12208</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>14631; 29585</t>
+          <t>10091; 23285</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4955; 15471</t>
+          <t>9111; 21078</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>10961; 24967</t>
+          <t>6135; 16248</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>11912; 25882</t>
+          <t>11491; 24729</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>27813; 48487</t>
+          <t>27891; 47872</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>16563; 32377</t>
+          <t>16441; 33063</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>19742; 36971</t>
+          <t>18650; 33949</t>
         </is>
       </c>
     </row>
@@ -2341,42 +2341,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>88</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>85</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>77</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2409,42 +2409,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>47392</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>63560</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>48482</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>55404</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>43878</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>61292</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>55726</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>47272</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>47392</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>63560</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>48482</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>59103</t>
+          <t>46649</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>106375</t>
+          <t>102053</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>34365; 55556</t>
+          <t>37145; 58298</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>49428; 74848</t>
+          <t>51375; 77387</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>44619; 68026</t>
+          <t>37665; 59976</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>37016; 58539</t>
+          <t>43666; 70112</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>37521; 58690</t>
+          <t>34308; 55512</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>52770; 77354</t>
+          <t>50093; 73802</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>38294; 60359</t>
+          <t>43970; 67739</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>45885; 72733</t>
+          <t>36345; 59025</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>78269; 107397</t>
+          <t>76421; 106506</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>107955; 144490</t>
+          <t>109361; 146480</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>89092; 121457</t>
+          <t>87932; 121156</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>90023; 125932</t>
+          <t>85971; 120273</t>
         </is>
       </c>
     </row>
